--- a/水钢设备到位情况统计.xlsx
+++ b/水钢设备到位情况统计.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wk-sh\Desktop\git版本管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900C168A-37F3-45D9-AEB5-11377B587338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23B5DDDA-DD5B-43AF-8178-B1CDF8B3C10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{77450A8B-85D4-4DE1-B7EC-F898364C8762}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="15340" windowHeight="8170" xr2:uid="{77450A8B-85D4-4DE1-B7EC-F898364C8762}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="26">
   <si>
     <t>设备</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -118,24 +119,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>均热段上部煤气流量</t>
-  </si>
-  <si>
-    <t>均热段下部煤气流量</t>
-  </si>
-  <si>
-    <t>加热段下部煤气流量</t>
-  </si>
-  <si>
-    <t>均热段上部空气流量</t>
-  </si>
-  <si>
-    <t>均热段下部空气流量</t>
-  </si>
-  <si>
-    <t>加热段下部空气流量</t>
-  </si>
-  <si>
     <t>请核对数量以及设备名称，</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -145,6 +128,18 @@
   </si>
   <si>
     <t>到位栏目就写是、否、不提供</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三台炉子加热段上共计12个（煤气与空气）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -205,12 +200,8 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -219,23 +210,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -615,11 +602,14 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>26</v>
+      <c r="G2" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -635,11 +625,14 @@
       <c r="D3" t="s">
         <v>9</v>
       </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>27</v>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -655,11 +648,14 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>28</v>
+      <c r="G4" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -675,10 +671,13 @@
       <c r="D5" t="s">
         <v>9</v>
       </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -693,10 +692,13 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="4"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -711,10 +713,13 @@
       <c r="D7" t="s">
         <v>9</v>
       </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="4"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -729,10 +734,13 @@
       <c r="D8" t="s">
         <v>9</v>
       </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="4"/>
+      <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -747,10 +755,13 @@
       <c r="D9" t="s">
         <v>18</v>
       </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="4"/>
+      <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -765,10 +776,13 @@
       <c r="D10" t="s">
         <v>18</v>
       </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="4"/>
+      <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -783,10 +797,13 @@
       <c r="D11" t="s">
         <v>6</v>
       </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="4"/>
+      <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -801,280 +818,79 @@
       <c r="D12" t="s">
         <v>6</v>
       </c>
+      <c r="E12" t="s">
+        <v>24</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="4"/>
+      <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="4"/>
+      <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="4"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25" t="s">
-        <v>6</v>
-      </c>
-      <c r="G25" s="4"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26" t="s">
-        <v>6</v>
-      </c>
-      <c r="G26" s="4"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27" t="s">
-        <v>6</v>
-      </c>
-      <c r="G27" s="4"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G28" s="4"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="4"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30" t="s">
-        <v>6</v>
-      </c>
-      <c r="G30" s="4"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G30" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
